--- a/Test Results/Android/Android_Appium_Report_LATEST.xlsx
+++ b/Test Results/Android/Android_Appium_Report_LATEST.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-09-12 08:33</t>
+          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-09-14 09:45</t>
         </is>
       </c>
     </row>

--- a/Test Results/Android/Android_Appium_Report_LATEST.xlsx
+++ b/Test Results/Android/Android_Appium_Report_LATEST.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-09-14 09:45</t>
+          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-09-15 09:20</t>
         </is>
       </c>
     </row>

--- a/Test Results/Android/Android_Appium_Report_LATEST.xlsx
+++ b/Test Results/Android/Android_Appium_Report_LATEST.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-09-15 09:20</t>
+          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-09-16 09:13</t>
         </is>
       </c>
     </row>

--- a/Test Results/Android/Android_Appium_Report_LATEST.xlsx
+++ b/Test Results/Android/Android_Appium_Report_LATEST.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-09-16 09:13</t>
+          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-09-17 09:21</t>
         </is>
       </c>
     </row>

--- a/Test Results/Android/Android_Appium_Report_LATEST.xlsx
+++ b/Test Results/Android/Android_Appium_Report_LATEST.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-09-17 09:21</t>
+          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-09-18 08:56</t>
         </is>
       </c>
     </row>

--- a/Test Results/Android/Android_Appium_Report_LATEST.xlsx
+++ b/Test Results/Android/Android_Appium_Report_LATEST.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-09-18 08:56</t>
+          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-09-19 08:43</t>
         </is>
       </c>
     </row>

--- a/Test Results/Android/Android_Appium_Report_LATEST.xlsx
+++ b/Test Results/Android/Android_Appium_Report_LATEST.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-09-19 08:43</t>
+          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-09-20 09:12</t>
         </is>
       </c>
     </row>

--- a/Test Results/Android/Android_Appium_Report_LATEST.xlsx
+++ b/Test Results/Android/Android_Appium_Report_LATEST.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-09-20 09:12</t>
+          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-09-21 09:50</t>
         </is>
       </c>
     </row>

--- a/Test Results/Android/Android_Appium_Report_LATEST.xlsx
+++ b/Test Results/Android/Android_Appium_Report_LATEST.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-09-21 09:50</t>
+          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-09-22 09:13</t>
         </is>
       </c>
     </row>

--- a/Test Results/Android/Android_Appium_Report_LATEST.xlsx
+++ b/Test Results/Android/Android_Appium_Report_LATEST.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-09-22 09:13</t>
+          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-09-23 09:14</t>
         </is>
       </c>
     </row>

--- a/Test Results/Android/Android_Appium_Report_LATEST.xlsx
+++ b/Test Results/Android/Android_Appium_Report_LATEST.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-09-23 09:14</t>
+          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-09-24 09:12</t>
         </is>
       </c>
     </row>

--- a/Test Results/Android/Android_Appium_Report_LATEST.xlsx
+++ b/Test Results/Android/Android_Appium_Report_LATEST.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-09-24 09:12</t>
+          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-09-25 09:31</t>
         </is>
       </c>
     </row>

--- a/Test Results/Android/Android_Appium_Report_LATEST.xlsx
+++ b/Test Results/Android/Android_Appium_Report_LATEST.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-09-25 09:31</t>
+          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-09-26 09:16</t>
         </is>
       </c>
     </row>

--- a/Test Results/Android/Android_Appium_Report_LATEST.xlsx
+++ b/Test Results/Android/Android_Appium_Report_LATEST.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-09-26 09:16</t>
+          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-09-27 09:56</t>
         </is>
       </c>
     </row>

--- a/Test Results/Android/Android_Appium_Report_LATEST.xlsx
+++ b/Test Results/Android/Android_Appium_Report_LATEST.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-09-27 09:56</t>
+          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-09-28 10:46</t>
         </is>
       </c>
     </row>

--- a/Test Results/Android/Android_Appium_Report_LATEST.xlsx
+++ b/Test Results/Android/Android_Appium_Report_LATEST.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-09-28 10:46</t>
+          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-09-29 10:35</t>
         </is>
       </c>
     </row>

--- a/Test Results/Android/Android_Appium_Report_LATEST.xlsx
+++ b/Test Results/Android/Android_Appium_Report_LATEST.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-09-29 10:35</t>
+          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-09-30 10:24</t>
         </is>
       </c>
     </row>

--- a/Test Results/Android/Android_Appium_Report_LATEST.xlsx
+++ b/Test Results/Android/Android_Appium_Report_LATEST.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-09-30 10:24</t>
+          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-10-01 10:51</t>
         </is>
       </c>
     </row>

--- a/Test Results/Android/Android_Appium_Report_LATEST.xlsx
+++ b/Test Results/Android/Android_Appium_Report_LATEST.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-10-01 10:51</t>
+          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-10-02 10:25</t>
         </is>
       </c>
     </row>

--- a/Test Results/Android/Android_Appium_Report_LATEST.xlsx
+++ b/Test Results/Android/Android_Appium_Report_LATEST.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-10-02 10:25</t>
+          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-10-03 09:47</t>
         </is>
       </c>
     </row>

--- a/Test Results/Android/Android_Appium_Report_LATEST.xlsx
+++ b/Test Results/Android/Android_Appium_Report_LATEST.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-10-03 09:47</t>
+          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-10-04 10:30</t>
         </is>
       </c>
     </row>

--- a/Test Results/Android/Android_Appium_Report_LATEST.xlsx
+++ b/Test Results/Android/Android_Appium_Report_LATEST.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-10-04 10:30</t>
+          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-10-05 11:21</t>
         </is>
       </c>
     </row>

--- a/Test Results/Android/Android_Appium_Report_LATEST.xlsx
+++ b/Test Results/Android/Android_Appium_Report_LATEST.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-10-05 11:21</t>
+          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-10-06 11:10</t>
         </is>
       </c>
     </row>

--- a/Test Results/Android/Android_Appium_Report_LATEST.xlsx
+++ b/Test Results/Android/Android_Appium_Report_LATEST.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-10-06 11:10</t>
+          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-10-07 10:59</t>
         </is>
       </c>
     </row>

--- a/Test Results/Android/Android_Appium_Report_LATEST.xlsx
+++ b/Test Results/Android/Android_Appium_Report_LATEST.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-10-07 10:59</t>
+          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-10-08 11:16</t>
         </is>
       </c>
     </row>

--- a/Test Results/Android/Android_Appium_Report_LATEST.xlsx
+++ b/Test Results/Android/Android_Appium_Report_LATEST.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-10-08 11:16</t>
+          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-10-09 11:14</t>
         </is>
       </c>
     </row>

--- a/Test Results/Android/Android_Appium_Report_LATEST.xlsx
+++ b/Test Results/Android/Android_Appium_Report_LATEST.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-10-09 11:14</t>
+          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-10-10 10:32</t>
         </is>
       </c>
     </row>

--- a/Test Results/Android/Android_Appium_Report_LATEST.xlsx
+++ b/Test Results/Android/Android_Appium_Report_LATEST.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-10-10 10:32</t>
+          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-10-11 10:44</t>
         </is>
       </c>
     </row>

--- a/Test Results/Android/Android_Appium_Report_LATEST.xlsx
+++ b/Test Results/Android/Android_Appium_Report_LATEST.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-10-11 10:44</t>
+          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-10-12 11:50</t>
         </is>
       </c>
     </row>

--- a/Test Results/Android/Android_Appium_Report_LATEST.xlsx
+++ b/Test Results/Android/Android_Appium_Report_LATEST.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-10-12 11:50</t>
+          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-10-13 11:38</t>
         </is>
       </c>
     </row>

--- a/Test Results/Android/Android_Appium_Report_LATEST.xlsx
+++ b/Test Results/Android/Android_Appium_Report_LATEST.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-10-13 11:38</t>
+          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-10-14 09:25</t>
         </is>
       </c>
     </row>

--- a/Test Results/Android/Android_Appium_Report_LATEST.xlsx
+++ b/Test Results/Android/Android_Appium_Report_LATEST.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-10-14 09:25</t>
+          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-10-15 09:03</t>
         </is>
       </c>
     </row>

--- a/Test Results/Android/Android_Appium_Report_LATEST.xlsx
+++ b/Test Results/Android/Android_Appium_Report_LATEST.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-10-15 09:03</t>
+          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-10-16 08:56</t>
         </is>
       </c>
     </row>

--- a/Test Results/Android/Android_Appium_Report_LATEST.xlsx
+++ b/Test Results/Android/Android_Appium_Report_LATEST.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-10-16 08:56</t>
+          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-10-17 08:27</t>
         </is>
       </c>
     </row>

--- a/Test Results/Android/Android_Appium_Report_LATEST.xlsx
+++ b/Test Results/Android/Android_Appium_Report_LATEST.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-10-17 08:27</t>
+          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-10-18 08:46</t>
         </is>
       </c>
     </row>

--- a/Test Results/Android/Android_Appium_Report_LATEST.xlsx
+++ b/Test Results/Android/Android_Appium_Report_LATEST.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-10-18 08:46</t>
+          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-10-19 09:47</t>
         </is>
       </c>
     </row>

--- a/Test Results/Android/Android_Appium_Report_LATEST.xlsx
+++ b/Test Results/Android/Android_Appium_Report_LATEST.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-10-19 09:47</t>
+          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-10-20 09:19</t>
         </is>
       </c>
     </row>

--- a/Test Results/Android/Android_Appium_Report_LATEST.xlsx
+++ b/Test Results/Android/Android_Appium_Report_LATEST.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-10-20 09:19</t>
+          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-10-21 09:16</t>
         </is>
       </c>
     </row>

--- a/Test Results/Android/Android_Appium_Report_LATEST.xlsx
+++ b/Test Results/Android/Android_Appium_Report_LATEST.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-10-21 09:16</t>
+          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-10-22 09:19</t>
         </is>
       </c>
     </row>

--- a/Test Results/Android/Android_Appium_Report_LATEST.xlsx
+++ b/Test Results/Android/Android_Appium_Report_LATEST.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-10-22 09:19</t>
+          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-10-23 09:14</t>
         </is>
       </c>
     </row>

--- a/Test Results/Android/Android_Appium_Report_LATEST.xlsx
+++ b/Test Results/Android/Android_Appium_Report_LATEST.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-10-23 09:14</t>
+          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-10-24 08:48</t>
         </is>
       </c>
     </row>

--- a/Test Results/Android/Android_Appium_Report_LATEST.xlsx
+++ b/Test Results/Android/Android_Appium_Report_LATEST.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-10-24 08:48</t>
+          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-10-25 09:04</t>
         </is>
       </c>
     </row>

--- a/Test Results/Android/Android_Appium_Report_LATEST.xlsx
+++ b/Test Results/Android/Android_Appium_Report_LATEST.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-10-25 09:04</t>
+          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-10-26 09:59</t>
         </is>
       </c>
     </row>

--- a/Test Results/Android/Android_Appium_Report_LATEST.xlsx
+++ b/Test Results/Android/Android_Appium_Report_LATEST.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-10-26 09:59</t>
+          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-10-27 09:43</t>
         </is>
       </c>
     </row>

--- a/Test Results/Android/Android_Appium_Report_LATEST.xlsx
+++ b/Test Results/Android/Android_Appium_Report_LATEST.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-10-27 09:43</t>
+          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-10-28 10:29</t>
         </is>
       </c>
     </row>

--- a/Test Results/Android/Android_Appium_Report_LATEST.xlsx
+++ b/Test Results/Android/Android_Appium_Report_LATEST.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-10-28 10:29</t>
+          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-10-29 10:49</t>
         </is>
       </c>
     </row>

--- a/Test Results/Android/Android_Appium_Report_LATEST.xlsx
+++ b/Test Results/Android/Android_Appium_Report_LATEST.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-10-29 10:49</t>
+          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-10-30 10:48</t>
         </is>
       </c>
     </row>

--- a/Test Results/Android/Android_Appium_Report_LATEST.xlsx
+++ b/Test Results/Android/Android_Appium_Report_LATEST.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-10-30 10:48</t>
+          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-10-31 10:17</t>
         </is>
       </c>
     </row>
